--- a/artfynd/A 13894-2026 artfynd.xlsx
+++ b/artfynd/A 13894-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132642250</v>
       </c>
       <c r="B2" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13894-2026 artfynd.xlsx
+++ b/artfynd/A 13894-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132642250</v>
       </c>
       <c r="B2" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13894-2026 artfynd.xlsx
+++ b/artfynd/A 13894-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132642250</v>
       </c>
       <c r="B2" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13894-2026 artfynd.xlsx
+++ b/artfynd/A 13894-2026 artfynd.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Per Muhr, Thomas Arnström</t>
+          <t>Per Muhr, Thomas Arnström, Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 13894-2026 artfynd.xlsx
+++ b/artfynd/A 13894-2026 artfynd.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström, Petra Borgcrantz</t>
+          <t>Petra Borgcrantz, Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 13894-2026 artfynd.xlsx
+++ b/artfynd/A 13894-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132642250</v>
       </c>
       <c r="B2" t="n">
-        <v>58117</v>
+        <v>58134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
